--- a/testcase_new/用例梳理.xlsx
+++ b/testcase_new/用例梳理.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>目录</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -39,6 +39,14 @@
   </si>
   <si>
     <t>余婷嘉文</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdv/c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>梁雪望</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -90,74 +98,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -169,7 +109,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="CCE8CF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -446,7 +386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="C5:D7"/>
+  <dimension ref="C5:D8"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="28.375" customWidth="1"/>
@@ -477,6 +417,14 @@
         <v>5</v>
       </c>
     </row>
+    <row r="8" spans="3:4">
+      <c r="C8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/testcase_new/用例梳理.xlsx
+++ b/testcase_new/用例梳理.xlsx
@@ -16,7 +16,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="34">
+  <si>
+    <t>tdd/python/所有目录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>余婷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tdd/php/所有目录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>余婷嘉文</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdv\java\com\story\consistencyData</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
   <si>
     <t>目录</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -26,27 +46,110 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>tdd/python/所有目录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>余婷</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tdd/php/所有目录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>余婷嘉文</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sdv/c</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>梁雪望</t>
+    <t>sdv\java\com\story\consistencyCluster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄晓妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdv\php</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄晓妮/王文净</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdv\js\subCL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdv\js\aggregate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdv\js\sql</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\aggregate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\dataCompress</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\matches</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\rest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\sdbimprt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\sdbMigrate</t>
+  </si>
+  <si>
+    <t>story\js\selectorQuery</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\sql</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\sqlArithmetic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\sqlHint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\subCL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>集群管理相关</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大数据量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdv</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tdd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>java</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>php</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>包含集群管理、鉴权、事务、备份恢复等</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -54,7 +157,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -69,13 +172,35 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -87,13 +212,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -386,43 +516,202 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="C5:D8"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="3" max="3" width="28.375" customWidth="1"/>
-    <col min="4" max="4" width="12.125" customWidth="1"/>
+    <col min="3" max="3" width="44.375" customWidth="1"/>
+    <col min="4" max="4" width="16.5" customWidth="1"/>
+    <col min="5" max="5" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="3:4">
+    <row r="1" spans="1:5">
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
       <c r="C5" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="3:4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="C6" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="3:4">
+        <v>8</v>
+      </c>
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
       <c r="C7" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="3:4">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
       <c r="C8" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="C12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="C13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="C14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="C15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="3:4">
+      <c r="C17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="3:4">
+      <c r="C18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="3:4">
+      <c r="C19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="3:4">
+      <c r="C20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="3:4">
+      <c r="C21" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/testcase_new/用例梳理.xlsx
+++ b/testcase_new/用例梳理.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="38">
   <si>
     <t>tdd/python/所有目录</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -150,6 +150,22 @@
   </si>
   <si>
     <t>包含集群管理、鉴权、事务、备份恢复等</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdv</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>所有目录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>梁雪望</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -516,7 +532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="44.375" customWidth="1"/>
@@ -674,7 +690,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="3:4">
+    <row r="17" spans="1:4">
       <c r="C17" t="s">
         <v>20</v>
       </c>
@@ -682,7 +698,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="3:4">
+    <row r="18" spans="1:4">
       <c r="C18" t="s">
         <v>21</v>
       </c>
@@ -690,7 +706,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="3:4">
+    <row r="19" spans="1:4">
       <c r="C19" t="s">
         <v>22</v>
       </c>
@@ -698,7 +714,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="3:4">
+    <row r="20" spans="1:4">
       <c r="C20" t="s">
         <v>23</v>
       </c>
@@ -706,12 +722,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="3:4">
+    <row r="21" spans="1:4">
       <c r="C21" t="s">
         <v>24</v>
       </c>
       <c r="D21" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/testcase_new/用例梳理.xlsx
+++ b/testcase_new/用例梳理.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="44">
   <si>
     <t>tdd/python/所有目录</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -162,6 +162,30 @@
   </si>
   <si>
     <t>所有目录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>梁雪望</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbLobTool</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbLobTool_auth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jsonTypes</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -532,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="44.375" customWidth="1"/>
@@ -742,6 +766,36 @@
       </c>
       <c r="D23" t="s">
         <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" t="s">
+        <v>40</v>
+      </c>
+      <c r="D24" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="C25" t="s">
+        <v>41</v>
+      </c>
+      <c r="D25" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="C26" t="s">
+        <v>42</v>
+      </c>
+      <c r="D26" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/testcase_new/用例梳理.xlsx
+++ b/testcase_new/用例梳理.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="47">
   <si>
     <t>tdd/python/所有目录</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -190,6 +190,18 @@
   </si>
   <si>
     <t>梁雪望</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbLobTool_ssl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>梁雪望</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbLobTool_reliable</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -556,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="44.375" customWidth="1"/>
@@ -792,9 +804,25 @@
     </row>
     <row r="26" spans="1:4">
       <c r="C26" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="C27" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="C28" t="s">
         <v>42</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D28" t="s">
         <v>43</v>
       </c>
     </row>

--- a/testcase_new/用例梳理.xlsx
+++ b/testcase_new/用例梳理.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="57">
   <si>
     <t>tdd/python/所有目录</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -46,162 +46,202 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>黄晓妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdv\php</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄晓妮/王文净</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdv\js\subCL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdv\js\aggregate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdv\js\sql</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\aggregate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\dataCompress</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\matches</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\rest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\sdbimprt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\sdbMigrate</t>
+  </si>
+  <si>
+    <t>story\js\selectorQuery</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\sql</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\sqlArithmetic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\sqlHint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>集群管理相关</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大数据量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdv</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tdd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>java</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>php</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>包含集群管理、鉴权、事务、备份恢复等</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>所有目录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>梁雪望</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>梁雪望</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>梁雪望</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\subCL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\sdbLobTool</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\sdbLobTool_auth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\sdbLobTool_ssl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\sdbLobTool_reliable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\jsonTypes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\listCL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\dropCL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吴艳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\index</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\dropIndex</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\split</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\transaction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\cjson</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdv\js\split</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdv\js\transaction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>sdv\java\com\story\consistencyCluster</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>黄晓妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sdv\php</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黄晓妮/王文净</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sdv\js\subCL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sdv\js\aggregate</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sdv\js\sql</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>story\js\aggregate</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>story\js\dataCompress</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>story\js\matches</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>story\js\rest</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>story\js\sdbimprt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>story\js\sdbMigrate</t>
-  </si>
-  <si>
-    <t>story\js\selectorQuery</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>story\js\sql</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>story\js\sqlArithmetic</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>story\js\sqlHint</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>story\js\subCL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>集群管理相关</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>大数据量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sdv</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tdd</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>story</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>java</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>php</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>js</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>包含集群管理、鉴权、事务、备份恢复等</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sdv</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>c</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>所有目录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>梁雪望</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>story</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>js</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sdbLobTool</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sdbLobTool_auth</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>jsonTypes</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>梁雪望</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sdbLobTool_ssl</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>梁雪望</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sdbLobTool_reliable</t>
+    <t>story\java\com\sequoiadb\lob</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -280,6 +320,74 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -291,7 +399,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="CCE8CF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -568,7 +676,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="44.375" customWidth="1"/>
@@ -583,10 +691,13 @@
       <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="E1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
         <v>0</v>
@@ -603,227 +714,301 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" t="s">
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
         <v>4</v>
       </c>
-      <c r="D5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="C6" t="s">
-        <v>7</v>
-      </c>
       <c r="D6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="B7" t="s">
-        <v>31</v>
-      </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="B8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="E8" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:5">
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="C10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" t="s">
-        <v>32</v>
-      </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="C12" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="C13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="3:5">
+      <c r="C17" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="3:5">
+      <c r="C18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="3:5">
+      <c r="C19" t="s">
         <v>16</v>
       </c>
-      <c r="D13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="C14" t="s">
+      <c r="D19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="3:5">
+      <c r="C20" t="s">
         <v>17</v>
       </c>
-      <c r="D14" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="C15" t="s">
+      <c r="D20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="3:5">
+      <c r="C21" t="s">
         <v>18</v>
       </c>
-      <c r="D15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="C16" t="s">
+      <c r="D21" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="3:5">
+      <c r="C22" t="s">
         <v>19</v>
       </c>
-      <c r="D16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="C17" t="s">
+      <c r="D22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="3:5">
+      <c r="C23" t="s">
         <v>20</v>
       </c>
-      <c r="D17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="C18" t="s">
+      <c r="D23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="3:5">
+      <c r="C24" t="s">
         <v>21</v>
       </c>
-      <c r="D18" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="C19" t="s">
+      <c r="D24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="3:5">
+      <c r="C25" t="s">
         <v>22</v>
       </c>
-      <c r="D19" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="C20" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="C21" t="s">
-        <v>24</v>
-      </c>
-      <c r="D21" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" t="s">
-        <v>34</v>
-      </c>
-      <c r="B23" t="s">
+      <c r="D25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="3:5">
+      <c r="C26" t="s">
+        <v>38</v>
+      </c>
+      <c r="D26" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="3:5">
+      <c r="C27" t="s">
+        <v>39</v>
+      </c>
+      <c r="D27" t="s">
         <v>35</v>
       </c>
-      <c r="C23" t="s">
+    </row>
+    <row r="28" spans="3:5">
+      <c r="C28" t="s">
+        <v>40</v>
+      </c>
+      <c r="D28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="3:5">
+      <c r="C29" t="s">
+        <v>41</v>
+      </c>
+      <c r="D29" t="s">
         <v>36</v>
       </c>
-      <c r="D23" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" t="s">
-        <v>39</v>
-      </c>
-      <c r="C24" t="s">
-        <v>40</v>
-      </c>
-      <c r="D24" t="s">
+    </row>
+    <row r="30" spans="3:5">
+      <c r="C30" t="s">
+        <v>42</v>
+      </c>
+      <c r="D30" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="3:5">
+      <c r="C31" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="C25" t="s">
-        <v>41</v>
-      </c>
-      <c r="D25" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="C26" t="s">
+      <c r="D31" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="3:5">
+      <c r="C32" t="s">
         <v>44</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D32" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4">
+      <c r="C33" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="C27" t="s">
+      <c r="D33" t="s">
         <v>46</v>
       </c>
-      <c r="D27" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="C28" t="s">
-        <v>42</v>
-      </c>
-      <c r="D28" t="s">
-        <v>43</v>
+    </row>
+    <row r="34" spans="2:4">
+      <c r="C34" t="s">
+        <v>47</v>
+      </c>
+      <c r="D34" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4">
+      <c r="C35" t="s">
+        <v>48</v>
+      </c>
+      <c r="D35" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4">
+      <c r="C36" t="s">
+        <v>49</v>
+      </c>
+      <c r="D36" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4">
+      <c r="C37" t="s">
+        <v>50</v>
+      </c>
+      <c r="D37" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4">
+      <c r="C38" t="s">
+        <v>51</v>
+      </c>
+      <c r="D38" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4">
+      <c r="B39" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39" t="s">
+        <v>56</v>
+      </c>
+      <c r="D39" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/testcase_new/用例梳理.xlsx
+++ b/testcase_new/用例梳理.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="78">
   <si>
     <t>tdd/python/所有目录</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -242,6 +242,90 @@
   </si>
   <si>
     <t>story\java\com\sequoiadb\lob</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mthMatch_large_data</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赵育</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>decimal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mthMatch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>domain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dropCS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alterCL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>selectorSymbol</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>updateSymbol</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>metaOperation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\sdv\java\decimal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>移至story\java目录下并配置xml文件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdv\java\com\story\backup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>配置入sync.xml中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\sdv\java\com\story\clustermanager</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>配置入sync.xml中，建议最后跑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\sdv\java\com\story\basicoperation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>部分用例，不影响不需修改</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\sdv\java\com\story\metadata</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -320,74 +404,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -399,7 +415,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="CCE8CF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -676,7 +692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="44.375" customWidth="1"/>
@@ -952,7 +968,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="2:4">
+    <row r="33" spans="1:5">
       <c r="C33" t="s">
         <v>45</v>
       </c>
@@ -960,7 +976,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="34" spans="2:4">
+    <row r="34" spans="1:5">
       <c r="C34" t="s">
         <v>47</v>
       </c>
@@ -968,7 +984,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="2:4">
+    <row r="35" spans="1:5">
       <c r="C35" t="s">
         <v>48</v>
       </c>
@@ -976,7 +992,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="36" spans="2:4">
+    <row r="36" spans="1:5">
       <c r="C36" t="s">
         <v>49</v>
       </c>
@@ -984,7 +1000,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="37" spans="2:4">
+    <row r="37" spans="1:5">
       <c r="C37" t="s">
         <v>50</v>
       </c>
@@ -992,7 +1008,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="38" spans="2:4">
+    <row r="38" spans="1:5">
       <c r="C38" t="s">
         <v>51</v>
       </c>
@@ -1000,7 +1016,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="39" spans="2:4">
+    <row r="39" spans="1:5">
       <c r="B39" t="s">
         <v>55</v>
       </c>
@@ -1009,6 +1025,164 @@
       </c>
       <c r="D39" t="s">
         <v>46</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>27</v>
+      </c>
+      <c r="B41" t="s">
+        <v>30</v>
+      </c>
+      <c r="C41" t="s">
+        <v>57</v>
+      </c>
+      <c r="D41" t="s">
+        <v>58</v>
+      </c>
+      <c r="E41" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="C42" t="s">
+        <v>59</v>
+      </c>
+      <c r="D42" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="C43" t="s">
+        <v>60</v>
+      </c>
+      <c r="D43" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="C44" t="s">
+        <v>61</v>
+      </c>
+      <c r="D44" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="C45" t="s">
+        <v>62</v>
+      </c>
+      <c r="D45" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="C46" t="s">
+        <v>63</v>
+      </c>
+      <c r="D46" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="C47" t="s">
+        <v>64</v>
+      </c>
+      <c r="D47" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="C48" t="s">
+        <v>65</v>
+      </c>
+      <c r="D48" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="C49" t="s">
+        <v>66</v>
+      </c>
+      <c r="D49" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="C50" t="s">
+        <v>67</v>
+      </c>
+      <c r="D50" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" t="s">
+        <v>25</v>
+      </c>
+      <c r="B51" t="s">
+        <v>30</v>
+      </c>
+      <c r="C51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D51" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="B52" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" t="s">
+        <v>69</v>
+      </c>
+      <c r="D52" t="s">
+        <v>58</v>
+      </c>
+      <c r="E52" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="C53" t="s">
+        <v>71</v>
+      </c>
+      <c r="D53" t="s">
+        <v>58</v>
+      </c>
+      <c r="E53" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="C54" t="s">
+        <v>73</v>
+      </c>
+      <c r="D54" t="s">
+        <v>58</v>
+      </c>
+      <c r="E54" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="C55" t="s">
+        <v>75</v>
+      </c>
+      <c r="D55" t="s">
+        <v>58</v>
+      </c>
+      <c r="E55" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="C56" t="s">
+        <v>77</v>
+      </c>
+      <c r="D56" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/testcase_new/用例梳理.xlsx
+++ b/testcase_new/用例梳理.xlsx
@@ -34,10 +34,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>sdv\java\com\story\consistencyData</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>目录</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -233,10 +229,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>sdv\java\com\story\consistencyCluster</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>java</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -326,6 +318,14 @@
   </si>
   <si>
     <t>\sdv\java\com\story\metadata</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\java\com\sequoiadb\consistencyData</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\java\com\sequoiadb\consistencyCluster</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -702,18 +702,18 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="E1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
         <v>0</v>
@@ -732,457 +732,457 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>4</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="C7" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="B8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
         <v>8</v>
       </c>
-      <c r="D8" t="s">
-        <v>9</v>
-      </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="C10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="C11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="C12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="C13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
         <v>32</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>33</v>
-      </c>
-      <c r="D14" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D16" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="3:5">
       <c r="C17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D17" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="3:5">
       <c r="C18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="3:5">
       <c r="C19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="3:5">
       <c r="C20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D20" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="3:5">
       <c r="C21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D21" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="3:5">
       <c r="C22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D22" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="3:5">
       <c r="C23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D23" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="3:5">
       <c r="C24" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D24" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="3:5">
       <c r="C25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D25" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="3:5">
       <c r="C26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D26" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="3:5">
       <c r="C27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="3:5">
       <c r="C28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="3:5">
       <c r="C29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="3:5">
       <c r="C30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="3:5">
       <c r="C31" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" spans="3:5">
       <c r="C32" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="C33" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" t="s">
         <v>45</v>
-      </c>
-      <c r="D33" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="C34" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D34" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="C35" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D35" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="C36" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D36" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="C37" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="C38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="B39" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C39" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D39" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C41" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D41" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E41" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="C42" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D42" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="C43" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D43" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="C44" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D44" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="C45" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D45" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="C46" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D46" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="C47" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D47" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="C48" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D48" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="C49" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D49" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="C50" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D50" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B51" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C51" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D51" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="B52" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C52" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D52" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E52" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="C53" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D53" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E53" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="C54" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D54" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E54" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="C55" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D55" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E55" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="C56" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D56" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/testcase_new/用例梳理.xlsx
+++ b/testcase_new/用例梳理.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="93">
   <si>
     <t>tdd/python/所有目录</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -229,103 +229,163 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>story\java\com\sequoiadb\lob</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mthMatch_large_data</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赵育</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>decimal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mthMatch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>domain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dropCS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alterCL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>selectorSymbol</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>updateSymbol</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>metaOperation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\sdv\java\decimal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>移至story\java目录下并配置xml文件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdv\java\com\story\backup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>配置入sync.xml中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\sdv\java\com\story\clustermanager</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>配置入sync.xml中，建议最后跑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\sdv\java\com\story\basicoperation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>部分用例，不影响不需修改</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\sdv\java\com\story\metadata</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\java\com\sequoiadb\consistencyData</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\java\com\sequoiadb\consistencyCluster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdv</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>driver</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>java</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>story\java\com\sequoiadb\lob</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mthMatch_large_data</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>赵育</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>decimal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mthMatch</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>domain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createCS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dropCS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createCL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>alterCL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>selectorSymbol</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>updateSymbol</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>metaOperation</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>\sdv\java\decimal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>移至story\java目录下并配置xml文件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sdv\java\com\story\backup</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>配置入sync.xml中</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>\sdv\java\com\story\clustermanager</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>配置入sync.xml中，建议最后跑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>\sdv\java\com\story\basicoperation</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>部分用例，不影响不需修改</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>\sdv\java\com\story\metadata</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>story\java\com\sequoiadb\consistencyData</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>story\java\com\sequoiadb\consistencyCluster</t>
+    <t>numberlong</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陈思琴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>split</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lzw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lzwtransaction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>java</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bsontype</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>auth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>procedure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbserial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trnsaction</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -692,7 +752,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="44.375" customWidth="1"/>
@@ -738,7 +798,7 @@
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
         <v>6</v>
@@ -746,7 +806,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="C7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
         <v>6</v>
@@ -1016,17 +1076,6 @@
         <v>45</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
-      <c r="B39" t="s">
-        <v>53</v>
-      </c>
-      <c r="C39" t="s">
-        <v>54</v>
-      </c>
-      <c r="D39" t="s">
-        <v>45</v>
-      </c>
-    </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
         <v>26</v>
@@ -1035,10 +1084,10 @@
         <v>29</v>
       </c>
       <c r="C41" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D41" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E41" t="s">
         <v>23</v>
@@ -1046,88 +1095,88 @@
     </row>
     <row r="42" spans="1:5">
       <c r="C42" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="C43" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D43" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="C44" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D44" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="C45" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D45" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="C46" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="C47" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D47" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="C48" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D48" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="C49" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D49" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="C50" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D50" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="B51" t="s">
         <v>29</v>
       </c>
       <c r="C51" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D51" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -1135,54 +1184,158 @@
         <v>27</v>
       </c>
       <c r="C52" t="s">
+        <v>66</v>
+      </c>
+      <c r="D52" t="s">
+        <v>55</v>
+      </c>
+      <c r="E52" t="s">
         <v>67</v>
       </c>
-      <c r="D52" t="s">
-        <v>56</v>
-      </c>
-      <c r="E52" t="s">
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" t="s">
+        <v>78</v>
+      </c>
+      <c r="C53" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="C53" t="s">
+      <c r="D53" t="s">
+        <v>55</v>
+      </c>
+      <c r="E53" t="s">
         <v>69</v>
-      </c>
-      <c r="D53" t="s">
-        <v>56</v>
-      </c>
-      <c r="E53" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="C54" t="s">
+        <v>70</v>
+      </c>
+      <c r="D54" t="s">
+        <v>55</v>
+      </c>
+      <c r="E54" t="s">
         <v>71</v>
-      </c>
-      <c r="D54" t="s">
-        <v>56</v>
-      </c>
-      <c r="E54" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="C55" t="s">
+        <v>72</v>
+      </c>
+      <c r="D55" t="s">
+        <v>55</v>
+      </c>
+      <c r="E55" t="s">
         <v>73</v>
-      </c>
-      <c r="D55" t="s">
-        <v>56</v>
-      </c>
-      <c r="E55" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="C56" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D56" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="12.75" customHeight="1">
+      <c r="A58" t="s">
+        <v>78</v>
+      </c>
+      <c r="B58" t="s">
+        <v>86</v>
+      </c>
+      <c r="C58" t="s">
+        <v>87</v>
+      </c>
+      <c r="D58" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="12.75" customHeight="1">
+      <c r="C59" t="s">
+        <v>88</v>
+      </c>
+      <c r="D59" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="12.75" customHeight="1">
+      <c r="C60" t="s">
+        <v>89</v>
+      </c>
+      <c r="D60" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="12.75" customHeight="1">
+      <c r="C61" t="s">
+        <v>90</v>
+      </c>
+      <c r="D61" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="12.75" customHeight="1">
+      <c r="C62" t="s">
+        <v>91</v>
+      </c>
+      <c r="D62" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="12.75" customHeight="1">
+      <c r="C63" t="s">
+        <v>92</v>
+      </c>
+      <c r="D63" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="12.75" customHeight="1"/>
+    <row r="65" spans="1:4">
+      <c r="A65" t="s">
+        <v>79</v>
+      </c>
+      <c r="B65" t="s">
+        <v>80</v>
+      </c>
+      <c r="C65" t="s">
+        <v>53</v>
+      </c>
+      <c r="D65" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="C66" t="s">
+        <v>81</v>
+      </c>
+      <c r="D66" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="C67" t="s">
+        <v>83</v>
+      </c>
+      <c r="D67" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="C68" t="s">
+        <v>84</v>
+      </c>
+      <c r="D68" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="C69" t="s">
+        <v>85</v>
+      </c>
+      <c r="D69" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/testcase_new/用例梳理.xlsx
+++ b/testcase_new/用例梳理.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="96">
   <si>
     <t>tdd/python/所有目录</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -333,59 +333,71 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>java</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>numberlong</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陈思琴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>split</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lzw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lzwtransaction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>java</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bsontype</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>auth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>procedure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbserial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trnsaction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>story</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>java</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>numberlong</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>陈思琴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>split</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>lzw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>lzwtransaction</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>java</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bsontype</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>auth</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>procedure</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sdb</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sdbserial</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>trnsaction</t>
+    <t>cpp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>所有目录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>梁雪望</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -393,7 +405,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -425,6 +437,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -454,9 +474,10 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -752,7 +773,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="44.375" customWidth="1"/>
@@ -790,51 +811,59 @@
         <v>3</v>
       </c>
     </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D5" t="s">
+        <v>6</v>
+      </c>
+    </row>
     <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" t="s">
-        <v>27</v>
-      </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
         <v>6</v>
       </c>
+      <c r="E6" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="7" spans="1:5">
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="B8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="B9" t="s">
-        <v>29</v>
-      </c>
       <c r="C9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" t="s">
         <v>6</v>
@@ -842,7 +871,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="C10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D10" t="s">
         <v>6</v>
@@ -850,179 +879,176 @@
     </row>
     <row r="11" spans="1:5">
       <c r="C11" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
-        <v>6</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="C12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="C13" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" t="s">
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="C15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="C16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="3:4">
+      <c r="C17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="3:4">
+      <c r="C18" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="3:4">
+      <c r="C19" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="3:4">
+      <c r="C20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="3:4">
+      <c r="C21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="3:4">
+      <c r="C22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="3:4">
+      <c r="C23" t="s">
+        <v>21</v>
+      </c>
+      <c r="D23" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="3:4">
+      <c r="C24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="3:4">
+      <c r="C25" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="3:4">
+      <c r="C26" t="s">
+        <v>39</v>
+      </c>
+      <c r="D26" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="3:4">
+      <c r="C27" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="3:4">
+      <c r="C28" t="s">
+        <v>41</v>
+      </c>
+      <c r="D28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="3:4">
+      <c r="C29" t="s">
+        <v>42</v>
+      </c>
+      <c r="D29" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="3:4">
+      <c r="C30" t="s">
+        <v>43</v>
+      </c>
+      <c r="D30" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
-      <c r="B14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" t="s">
-        <v>26</v>
-      </c>
-      <c r="B16" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="3:5">
-      <c r="C17" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E17" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="3:5">
-      <c r="C18" t="s">
-        <v>14</v>
-      </c>
-      <c r="D18" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="3:5">
-      <c r="C19" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="3:5">
-      <c r="C20" t="s">
-        <v>16</v>
-      </c>
-      <c r="D20" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="3:5">
-      <c r="C21" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="3:5">
-      <c r="C22" t="s">
-        <v>18</v>
-      </c>
-      <c r="D22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="3:5">
-      <c r="C23" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="3:5">
-      <c r="C24" t="s">
-        <v>20</v>
-      </c>
-      <c r="D24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="3:5">
-      <c r="C25" t="s">
-        <v>21</v>
-      </c>
-      <c r="D25" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="3:5">
-      <c r="C26" t="s">
-        <v>37</v>
-      </c>
-      <c r="D26" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="3:5">
-      <c r="C27" t="s">
-        <v>38</v>
-      </c>
-      <c r="D27" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" spans="3:5">
-      <c r="C28" t="s">
-        <v>39</v>
-      </c>
-      <c r="D28" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="29" spans="3:5">
-      <c r="C29" t="s">
-        <v>40</v>
-      </c>
-      <c r="D29" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="30" spans="3:5">
-      <c r="C30" t="s">
-        <v>41</v>
-      </c>
-      <c r="D30" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="31" spans="3:5">
+    <row r="31" spans="3:4">
       <c r="C31" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D31" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="32" spans="3:5">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" spans="3:4">
       <c r="C32" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D32" t="s">
         <v>45</v>
@@ -1030,7 +1056,7 @@
     </row>
     <row r="33" spans="1:5">
       <c r="C33" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D33" t="s">
         <v>45</v>
@@ -1038,7 +1064,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="C34" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D34" t="s">
         <v>45</v>
@@ -1046,7 +1072,7 @@
     </row>
     <row r="35" spans="1:5">
       <c r="C35" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D35" t="s">
         <v>45</v>
@@ -1054,48 +1080,56 @@
     </row>
     <row r="36" spans="1:5">
       <c r="C36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D36" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
-      <c r="C37" t="s">
-        <v>49</v>
-      </c>
-      <c r="D37" t="s">
-        <v>45</v>
-      </c>
-    </row>
     <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>26</v>
+      </c>
+      <c r="B38" t="s">
+        <v>29</v>
+      </c>
       <c r="C38" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D38" t="s">
-        <v>45</v>
+        <v>55</v>
+      </c>
+      <c r="E38" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="C39" t="s">
+        <v>56</v>
+      </c>
+      <c r="D39" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="C40" t="s">
+        <v>57</v>
+      </c>
+      <c r="D40" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" t="s">
-        <v>26</v>
-      </c>
-      <c r="B41" t="s">
-        <v>29</v>
-      </c>
       <c r="C41" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D41" t="s">
         <v>55</v>
-      </c>
-      <c r="E41" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="C42" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D42" t="s">
         <v>55</v>
@@ -1103,7 +1137,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="C43" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D43" t="s">
         <v>55</v>
@@ -1111,7 +1145,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="C44" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D44" t="s">
         <v>55</v>
@@ -1119,7 +1153,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="C45" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D45" t="s">
         <v>55</v>
@@ -1127,7 +1161,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="C46" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D46" t="s">
         <v>55</v>
@@ -1135,207 +1169,205 @@
     </row>
     <row r="47" spans="1:5">
       <c r="C47" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D47" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="48" spans="1:5">
+      <c r="A48" t="s">
+        <v>77</v>
+      </c>
+      <c r="B48" t="s">
+        <v>29</v>
+      </c>
       <c r="C48" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D48" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="49" spans="1:5">
+      <c r="B49" t="s">
+        <v>27</v>
+      </c>
       <c r="C49" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D49" t="s">
         <v>55</v>
       </c>
+      <c r="E49" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="50" spans="1:5">
+      <c r="A50" t="s">
+        <v>78</v>
+      </c>
       <c r="C50" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D50" t="s">
         <v>55</v>
       </c>
+      <c r="E50" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" t="s">
-        <v>77</v>
-      </c>
-      <c r="B51" t="s">
-        <v>29</v>
-      </c>
       <c r="C51" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D51" t="s">
         <v>55</v>
       </c>
+      <c r="E51" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="52" spans="1:5">
-      <c r="B52" t="s">
-        <v>27</v>
-      </c>
       <c r="C52" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D52" t="s">
         <v>55</v>
       </c>
       <c r="E52" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" t="s">
+      <c r="C53" t="s">
+        <v>74</v>
+      </c>
+      <c r="D53" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="12.75" customHeight="1">
+      <c r="A55" t="s">
         <v>78</v>
       </c>
-      <c r="C53" t="s">
-        <v>68</v>
-      </c>
-      <c r="D53" t="s">
-        <v>55</v>
-      </c>
-      <c r="E53" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="C54" t="s">
-        <v>70</v>
-      </c>
-      <c r="D54" t="s">
-        <v>55</v>
-      </c>
-      <c r="E54" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
+      <c r="B55" t="s">
+        <v>85</v>
+      </c>
       <c r="C55" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="D55" t="s">
-        <v>55</v>
-      </c>
-      <c r="E55" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="12.75" customHeight="1">
       <c r="C56" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="D56" t="s">
-        <v>55</v>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="12.75" customHeight="1">
+      <c r="C57" t="s">
+        <v>88</v>
+      </c>
+      <c r="D57" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="12.75" customHeight="1">
-      <c r="A58" t="s">
-        <v>78</v>
-      </c>
-      <c r="B58" t="s">
-        <v>86</v>
-      </c>
       <c r="C58" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D58" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="12.75" customHeight="1">
       <c r="C59" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D59" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="12.75" customHeight="1">
       <c r="C60" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D60" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="12.75" customHeight="1">
+      <c r="B61" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" t="s">
+        <v>32</v>
+      </c>
+      <c r="D61" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="12.75" customHeight="1">
+      <c r="B62" t="s">
+        <v>93</v>
+      </c>
+      <c r="C62" t="s">
+        <v>94</v>
+      </c>
+      <c r="D62" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="12.75" customHeight="1"/>
+    <row r="64" spans="1:5">
+      <c r="A64" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B64" t="s">
+        <v>79</v>
+      </c>
+      <c r="C64" t="s">
+        <v>53</v>
+      </c>
+      <c r="D64" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="65" spans="3:4">
+      <c r="C65" t="s">
+        <v>80</v>
+      </c>
+      <c r="D65" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="66" spans="3:4">
+      <c r="C66" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" ht="12.75" customHeight="1">
-      <c r="C61" t="s">
-        <v>90</v>
-      </c>
-      <c r="D61" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" ht="12.75" customHeight="1">
-      <c r="C62" t="s">
-        <v>91</v>
-      </c>
-      <c r="D62" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" ht="12.75" customHeight="1">
-      <c r="C63" t="s">
-        <v>92</v>
-      </c>
-      <c r="D63" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" ht="12.75" customHeight="1"/>
-    <row r="65" spans="1:4">
-      <c r="A65" t="s">
-        <v>79</v>
-      </c>
-      <c r="B65" t="s">
-        <v>80</v>
-      </c>
-      <c r="C65" t="s">
-        <v>53</v>
-      </c>
-      <c r="D65" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
-      <c r="C66" t="s">
+      <c r="D66" t="s">
         <v>81</v>
       </c>
-      <c r="D66" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
+    </row>
+    <row r="67" spans="3:4">
       <c r="C67" t="s">
         <v>83</v>
       </c>
       <c r="D67" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="68" spans="3:4">
       <c r="C68" t="s">
         <v>84</v>
       </c>
       <c r="D68" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="C69" t="s">
-        <v>85</v>
-      </c>
-      <c r="D69" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/testcase_new/用例梳理.xlsx
+++ b/testcase_new/用例梳理.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="99">
   <si>
     <t>tdd/python/所有目录</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -398,6 +398,18 @@
   </si>
   <si>
     <t>梁雪望</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\jsObject</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>梁雪望</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\jsObjectSync</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -773,7 +785,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="44.375" customWidth="1"/>
@@ -1086,42 +1098,42 @@
         <v>45</v>
       </c>
     </row>
+    <row r="37" spans="1:5">
+      <c r="C37" t="s">
+        <v>96</v>
+      </c>
+      <c r="D37" t="s">
+        <v>97</v>
+      </c>
+    </row>
     <row r="38" spans="1:5">
-      <c r="A38" t="s">
+      <c r="C38" t="s">
+        <v>98</v>
+      </c>
+      <c r="D38" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
         <v>26</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B40" t="s">
         <v>29</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C40" t="s">
         <v>54</v>
       </c>
-      <c r="D38" t="s">
-        <v>55</v>
-      </c>
-      <c r="E38" t="s">
+      <c r="D40" t="s">
+        <v>55</v>
+      </c>
+      <c r="E40" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="C39" t="s">
-        <v>56</v>
-      </c>
-      <c r="D39" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="C40" t="s">
-        <v>57</v>
-      </c>
-      <c r="D40" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="C41" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D41" t="s">
         <v>55</v>
@@ -1129,7 +1141,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="C42" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D42" t="s">
         <v>55</v>
@@ -1137,7 +1149,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="C43" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D43" t="s">
         <v>55</v>
@@ -1145,7 +1157,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="C44" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D44" t="s">
         <v>55</v>
@@ -1153,7 +1165,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="C45" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D45" t="s">
         <v>55</v>
@@ -1161,7 +1173,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="C46" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D46" t="s">
         <v>55</v>
@@ -1169,109 +1181,109 @@
     </row>
     <row r="47" spans="1:5">
       <c r="C47" t="s">
+        <v>62</v>
+      </c>
+      <c r="D47" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="C48" t="s">
+        <v>63</v>
+      </c>
+      <c r="D48" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="C49" t="s">
         <v>64</v>
       </c>
-      <c r="D47" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" t="s">
-        <v>77</v>
-      </c>
-      <c r="B48" t="s">
-        <v>29</v>
-      </c>
-      <c r="C48" t="s">
-        <v>65</v>
-      </c>
-      <c r="D48" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="B49" t="s">
-        <v>27</v>
-      </c>
-      <c r="C49" t="s">
-        <v>66</v>
-      </c>
       <c r="D49" t="s">
         <v>55</v>
-      </c>
-      <c r="E49" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
+        <v>77</v>
+      </c>
+      <c r="B50" t="s">
+        <v>29</v>
+      </c>
+      <c r="C50" t="s">
+        <v>65</v>
+      </c>
+      <c r="D50" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="B51" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" t="s">
+        <v>66</v>
+      </c>
+      <c r="D51" t="s">
+        <v>55</v>
+      </c>
+      <c r="E51" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" t="s">
         <v>78</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C52" t="s">
         <v>68</v>
       </c>
-      <c r="D50" t="s">
-        <v>55</v>
-      </c>
-      <c r="E50" t="s">
+      <c r="D52" t="s">
+        <v>55</v>
+      </c>
+      <c r="E52" t="s">
         <v>69</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="C51" t="s">
-        <v>70</v>
-      </c>
-      <c r="D51" t="s">
-        <v>55</v>
-      </c>
-      <c r="E51" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="C52" t="s">
-        <v>72</v>
-      </c>
-      <c r="D52" t="s">
-        <v>55</v>
-      </c>
-      <c r="E52" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="C53" t="s">
+        <v>70</v>
+      </c>
+      <c r="D53" t="s">
+        <v>55</v>
+      </c>
+      <c r="E53" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="C54" t="s">
+        <v>72</v>
+      </c>
+      <c r="D54" t="s">
+        <v>55</v>
+      </c>
+      <c r="E54" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="C55" t="s">
         <v>74</v>
       </c>
-      <c r="D53" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="12.75" customHeight="1">
-      <c r="A55" t="s">
+      <c r="D55" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="12.75" customHeight="1">
+      <c r="A57" t="s">
         <v>78</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B57" t="s">
         <v>85</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C57" t="s">
         <v>86</v>
-      </c>
-      <c r="D55" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" ht="12.75" customHeight="1">
-      <c r="C56" t="s">
-        <v>87</v>
-      </c>
-      <c r="D56" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" ht="12.75" customHeight="1">
-      <c r="C57" t="s">
-        <v>88</v>
       </c>
       <c r="D57" t="s">
         <v>81</v>
@@ -1279,7 +1291,7 @@
     </row>
     <row r="58" spans="1:5" ht="12.75" customHeight="1">
       <c r="C58" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D58" t="s">
         <v>81</v>
@@ -1287,7 +1299,7 @@
     </row>
     <row r="59" spans="1:5" ht="12.75" customHeight="1">
       <c r="C59" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D59" t="s">
         <v>81</v>
@@ -1295,78 +1307,94 @@
     </row>
     <row r="60" spans="1:5" ht="12.75" customHeight="1">
       <c r="C60" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D60" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="12.75" customHeight="1">
-      <c r="B61" t="s">
+      <c r="C61" t="s">
+        <v>90</v>
+      </c>
+      <c r="D61" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="12.75" customHeight="1">
+      <c r="C62" t="s">
+        <v>91</v>
+      </c>
+      <c r="D62" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="12.75" customHeight="1">
+      <c r="B63" t="s">
         <v>31</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C63" t="s">
         <v>32</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D63" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="12.75" customHeight="1">
-      <c r="B62" t="s">
+    <row r="64" spans="1:5" ht="12.75" customHeight="1">
+      <c r="B64" t="s">
         <v>93</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C64" t="s">
         <v>94</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D64" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="12.75" customHeight="1"/>
-    <row r="64" spans="1:5">
-      <c r="A64" s="2" t="s">
+    <row r="65" spans="1:4" ht="12.75" customHeight="1"/>
+    <row r="66" spans="1:4">
+      <c r="A66" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B66" t="s">
         <v>79</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C66" t="s">
         <v>53</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D66" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="65" spans="3:4">
-      <c r="C65" t="s">
+    <row r="67" spans="1:4">
+      <c r="C67" t="s">
         <v>80</v>
-      </c>
-      <c r="D65" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="66" spans="3:4">
-      <c r="C66" t="s">
-        <v>82</v>
-      </c>
-      <c r="D66" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="67" spans="3:4">
-      <c r="C67" t="s">
-        <v>83</v>
       </c>
       <c r="D67" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="68" spans="3:4">
+    <row r="68" spans="1:4">
       <c r="C68" t="s">
+        <v>82</v>
+      </c>
+      <c r="D68" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="C69" t="s">
+        <v>83</v>
+      </c>
+      <c r="D69" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="C70" t="s">
         <v>84</v>
       </c>
-      <c r="D68" t="s">
+      <c r="D70" t="s">
         <v>81</v>
       </c>
     </row>

--- a/testcase_new/用例梳理.xlsx
+++ b/testcase_new/用例梳理.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="107">
   <si>
     <t>tdd/python/所有目录</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -410,6 +410,38 @@
   </si>
   <si>
     <t>story\js\jsObjectSync</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\java\com\sequoiadb\split</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\java\com\sequoiadb\subcl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄俏辉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\java\com\sequoiadb\transaction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\java\com\sequoiadb\serial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdv</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>java</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdv\java\com\sequoiadb\split</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -785,7 +817,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="44.375" customWidth="1"/>
@@ -1396,6 +1428,52 @@
       </c>
       <c r="D70" t="s">
         <v>81</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="C71" t="s">
+        <v>99</v>
+      </c>
+      <c r="D71" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="C72" t="s">
+        <v>100</v>
+      </c>
+      <c r="D72" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="C73" t="s">
+        <v>102</v>
+      </c>
+      <c r="D73" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="C74" t="s">
+        <v>103</v>
+      </c>
+      <c r="D74" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" t="s">
+        <v>104</v>
+      </c>
+      <c r="B76" t="s">
+        <v>105</v>
+      </c>
+      <c r="C76" t="s">
+        <v>106</v>
+      </c>
+      <c r="D76" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/testcase_new/用例梳理.xlsx
+++ b/testcase_new/用例梳理.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="117">
   <si>
     <t>tdd/python/所有目录</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -442,6 +442,46 @@
   </si>
   <si>
     <t>sdv\java\com\sequoiadb\split</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\procedures</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\query</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\rest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\truncate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\update</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdv</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story\js\basicopration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>余婷</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -529,6 +569,74 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -540,7 +648,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="CCE8CF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -817,7 +925,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E83"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="44.375" customWidth="1"/>
@@ -855,373 +963,385 @@
         <v>3</v>
       </c>
     </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D4" t="s">
+        <v>116</v>
+      </c>
+    </row>
     <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" t="s">
-        <v>27</v>
-      </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>6</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="C6" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="D6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" t="s">
-        <v>22</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="B7" t="s">
-        <v>28</v>
-      </c>
       <c r="C7" t="s">
-        <v>7</v>
+        <v>112</v>
       </c>
       <c r="D7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" t="s">
-        <v>30</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
       <c r="C8" t="s">
-        <v>10</v>
+        <v>113</v>
       </c>
       <c r="D8" t="s">
-        <v>6</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>114</v>
+      </c>
+      <c r="B9" t="s">
+        <v>108</v>
+      </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>115</v>
       </c>
       <c r="D9" t="s">
-        <v>6</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="C10" t="s">
-        <v>9</v>
+        <v>111</v>
       </c>
       <c r="D10" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
-      <c r="C11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="C12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" t="s">
-        <v>45</v>
+    <row r="13" spans="1:5">
+      <c r="C13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
       <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="B15" t="s">
         <v>29</v>
       </c>
-      <c r="C14" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
       <c r="C15" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D15" t="s">
         <v>6</v>
       </c>
-      <c r="E15" t="s">
-        <v>23</v>
-      </c>
     </row>
     <row r="16" spans="1:5">
       <c r="C16" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D16" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="3:4">
+    <row r="17" spans="1:5">
       <c r="C17" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D17" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="3:4">
+    <row r="18" spans="1:5">
       <c r="C18" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="D18" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="3:4">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="C19" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="D19" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="3:4">
-      <c r="C20" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="3:4">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" t="s">
+        <v>29</v>
+      </c>
       <c r="C21" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D21" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="3:4">
+    <row r="22" spans="1:5">
       <c r="C22" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D22" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="23" spans="3:4">
+      <c r="E22" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="C23" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D23" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="3:4">
+    <row r="24" spans="1:5">
       <c r="C24" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D24" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="3:4">
+    <row r="25" spans="1:5">
       <c r="C25" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="C26" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="C27" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="C28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="C29" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="C30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="C31" t="s">
+        <v>37</v>
+      </c>
+      <c r="D31" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="C32" t="s">
         <v>38</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D32" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="26" spans="3:4">
-      <c r="C26" t="s">
-        <v>39</v>
-      </c>
-      <c r="D26" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="27" spans="3:4">
-      <c r="C27" t="s">
-        <v>40</v>
-      </c>
-      <c r="D27" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="3:4">
-      <c r="C28" t="s">
-        <v>41</v>
-      </c>
-      <c r="D28" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="29" spans="3:4">
-      <c r="C29" t="s">
-        <v>42</v>
-      </c>
-      <c r="D29" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="30" spans="3:4">
-      <c r="C30" t="s">
-        <v>43</v>
-      </c>
-      <c r="D30" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="31" spans="3:4">
-      <c r="C31" t="s">
-        <v>44</v>
-      </c>
-      <c r="D31" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="32" spans="3:4">
-      <c r="C32" t="s">
-        <v>46</v>
-      </c>
-      <c r="D32" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="C33" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D33" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="C34" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D34" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="C35" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D35" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="C36" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D36" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="C37" t="s">
-        <v>96</v>
+        <v>43</v>
       </c>
       <c r="D37" t="s">
-        <v>97</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="C38" t="s">
-        <v>98</v>
+        <v>44</v>
       </c>
       <c r="D38" t="s">
-        <v>97</v>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="C39" t="s">
+        <v>46</v>
+      </c>
+      <c r="D39" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" t="s">
-        <v>26</v>
-      </c>
-      <c r="B40" t="s">
-        <v>29</v>
-      </c>
       <c r="C40" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D40" t="s">
-        <v>55</v>
-      </c>
-      <c r="E40" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="C41" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D41" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="C42" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D42" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="C43" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D43" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="C44" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="D44" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="C45" t="s">
-        <v>60</v>
+        <v>98</v>
       </c>
       <c r="D45" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="C46" t="s">
-        <v>61</v>
-      </c>
-      <c r="D46" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
     </row>
     <row r="47" spans="1:5">
+      <c r="A47" t="s">
+        <v>26</v>
+      </c>
+      <c r="B47" t="s">
+        <v>29</v>
+      </c>
       <c r="C47" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D47" t="s">
         <v>55</v>
       </c>
+      <c r="E47" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="48" spans="1:5">
       <c r="C48" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D48" t="s">
         <v>55</v>
@@ -1229,250 +1349,306 @@
     </row>
     <row r="49" spans="1:5">
       <c r="C49" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D49" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" t="s">
-        <v>77</v>
-      </c>
-      <c r="B50" t="s">
-        <v>29</v>
-      </c>
       <c r="C50" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D50" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="51" spans="1:5">
-      <c r="B51" t="s">
-        <v>27</v>
-      </c>
       <c r="C51" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D51" t="s">
         <v>55</v>
       </c>
-      <c r="E51" t="s">
-        <v>67</v>
-      </c>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" t="s">
-        <v>78</v>
-      </c>
       <c r="C52" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D52" t="s">
         <v>55</v>
       </c>
-      <c r="E52" t="s">
-        <v>69</v>
-      </c>
     </row>
     <row r="53" spans="1:5">
       <c r="C53" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="D53" t="s">
         <v>55</v>
       </c>
-      <c r="E53" t="s">
-        <v>71</v>
-      </c>
     </row>
     <row r="54" spans="1:5">
       <c r="C54" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D54" t="s">
         <v>55</v>
       </c>
-      <c r="E54" t="s">
-        <v>73</v>
-      </c>
     </row>
     <row r="55" spans="1:5">
       <c r="C55" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="D55" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="12.75" customHeight="1">
+    <row r="56" spans="1:5">
+      <c r="C56" t="s">
+        <v>64</v>
+      </c>
+      <c r="D56" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
       <c r="A57" t="s">
+        <v>77</v>
+      </c>
+      <c r="B57" t="s">
+        <v>29</v>
+      </c>
+      <c r="C57" t="s">
+        <v>65</v>
+      </c>
+      <c r="D57" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="B58" t="s">
+        <v>27</v>
+      </c>
+      <c r="C58" t="s">
+        <v>66</v>
+      </c>
+      <c r="D58" t="s">
+        <v>55</v>
+      </c>
+      <c r="E58" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" t="s">
         <v>78</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C59" t="s">
+        <v>68</v>
+      </c>
+      <c r="D59" t="s">
+        <v>55</v>
+      </c>
+      <c r="E59" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="C60" t="s">
+        <v>70</v>
+      </c>
+      <c r="D60" t="s">
+        <v>55</v>
+      </c>
+      <c r="E60" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="C61" t="s">
+        <v>72</v>
+      </c>
+      <c r="D61" t="s">
+        <v>55</v>
+      </c>
+      <c r="E61" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="C62" t="s">
+        <v>74</v>
+      </c>
+      <c r="D62" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="12.75" customHeight="1">
+      <c r="A64" t="s">
+        <v>78</v>
+      </c>
+      <c r="B64" t="s">
         <v>85</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C64" t="s">
         <v>86</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D64" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="12.75" customHeight="1">
-      <c r="C58" t="s">
+    <row r="65" spans="1:4" ht="12.75" customHeight="1">
+      <c r="C65" t="s">
         <v>87</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D65" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="12.75" customHeight="1">
-      <c r="C59" t="s">
+    <row r="66" spans="1:4" ht="12.75" customHeight="1">
+      <c r="C66" t="s">
         <v>88</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D66" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="12.75" customHeight="1">
-      <c r="C60" t="s">
+    <row r="67" spans="1:4" ht="12.75" customHeight="1">
+      <c r="C67" t="s">
         <v>89</v>
-      </c>
-      <c r="D60" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" ht="12.75" customHeight="1">
-      <c r="C61" t="s">
-        <v>90</v>
-      </c>
-      <c r="D61" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" ht="12.75" customHeight="1">
-      <c r="C62" t="s">
-        <v>91</v>
-      </c>
-      <c r="D62" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" ht="12.75" customHeight="1">
-      <c r="B63" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" t="s">
-        <v>32</v>
-      </c>
-      <c r="D63" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" ht="12.75" customHeight="1">
-      <c r="B64" t="s">
-        <v>93</v>
-      </c>
-      <c r="C64" t="s">
-        <v>94</v>
-      </c>
-      <c r="D64" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" ht="12.75" customHeight="1"/>
-    <row r="66" spans="1:4">
-      <c r="A66" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B66" t="s">
-        <v>79</v>
-      </c>
-      <c r="C66" t="s">
-        <v>53</v>
-      </c>
-      <c r="D66" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
-      <c r="C67" t="s">
-        <v>80</v>
       </c>
       <c r="D67" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="68" spans="1:4">
+    <row r="68" spans="1:4" ht="12.75" customHeight="1">
       <c r="C68" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D68" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="69" spans="1:4">
+    <row r="69" spans="1:4" ht="12.75" customHeight="1">
       <c r="C69" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D69" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="70" spans="1:4">
+    <row r="70" spans="1:4" ht="12.75" customHeight="1">
+      <c r="B70" t="s">
+        <v>31</v>
+      </c>
       <c r="C70" t="s">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="D70" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="12.75" customHeight="1">
+      <c r="B71" t="s">
+        <v>93</v>
+      </c>
       <c r="C71" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D71" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4">
-      <c r="C72" t="s">
-        <v>100</v>
-      </c>
-      <c r="D72" t="s">
-        <v>101</v>
-      </c>
-    </row>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="12.75" customHeight="1"/>
     <row r="73" spans="1:4">
+      <c r="A73" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B73" t="s">
+        <v>79</v>
+      </c>
       <c r="C73" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="D73" t="s">
-        <v>101</v>
+        <v>45</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="C74" t="s">
+        <v>80</v>
+      </c>
+      <c r="D74" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="C75" t="s">
+        <v>82</v>
+      </c>
+      <c r="D75" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="C76" t="s">
+        <v>83</v>
+      </c>
+      <c r="D76" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="C77" t="s">
+        <v>84</v>
+      </c>
+      <c r="D77" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="C78" t="s">
+        <v>99</v>
+      </c>
+      <c r="D78" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="C79" t="s">
+        <v>100</v>
+      </c>
+      <c r="D79" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="C80" t="s">
+        <v>102</v>
+      </c>
+      <c r="D80" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="C81" t="s">
         <v>103</v>
       </c>
-      <c r="D74" t="s">
+      <c r="D81" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="76" spans="1:4">
-      <c r="A76" t="s">
+    <row r="83" spans="1:4">
+      <c r="A83" t="s">
         <v>104</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B83" t="s">
         <v>105</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C83" t="s">
         <v>106</v>
       </c>
-      <c r="D76" t="s">
+      <c r="D83" t="s">
         <v>101</v>
       </c>
     </row>
